--- a/LoanOfficer-A/2023/113 inaobi.xlsx
+++ b/LoanOfficer-A/2023/113 inaobi.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>800</v>
+        <v>1400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>23200</v>
+        <v>22600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -990,9 +990,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45784</v>
+      </c>
+      <c r="C7" s="4">
+        <v>200</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1016,9 +1022,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45787</v>
+      </c>
+      <c r="C8" s="4">
+        <v>200</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1042,9 +1054,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45788</v>
+      </c>
+      <c r="C9" s="4">
+        <v>200</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>

--- a/LoanOfficer-A/2023/113 inaobi.xlsx
+++ b/LoanOfficer-A/2023/113 inaobi.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3000" windowWidth="20640" windowHeight="11760" activeTab="1"/>
   </bookViews>
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD20000.18-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="145621" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yyyy;@"/>
@@ -393,7 +393,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -428,7 +428,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1400</v>
+        <v>2600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>22600</v>
+        <v>21400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1086,9 +1086,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45824</v>
+      </c>
+      <c r="C10" s="4">
+        <v>200</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1112,9 +1118,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45825</v>
+      </c>
+      <c r="C11" s="4">
+        <v>200</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1138,9 +1150,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45828</v>
+      </c>
+      <c r="C12" s="4">
+        <v>200</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1164,9 +1182,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45830</v>
+      </c>
+      <c r="C13" s="4">
+        <v>200</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1190,9 +1214,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45833</v>
+      </c>
+      <c r="C14" s="4">
+        <v>200</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1216,9 +1246,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45841</v>
+      </c>
+      <c r="C15" s="4">
+        <v>200</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>

--- a/LoanOfficer-A/2023/113 inaobi.xlsx
+++ b/LoanOfficer-A/2023/113 inaobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2600</v>
+        <v>3200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>21400</v>
+        <v>20800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1278,9 +1278,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45845</v>
+      </c>
+      <c r="C16" s="4">
+        <v>200</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1304,9 +1310,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45846</v>
+      </c>
+      <c r="C17" s="4">
+        <v>200</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1330,9 +1342,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45847</v>
+      </c>
+      <c r="C18" s="4">
+        <v>200</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>

--- a/LoanOfficer-A/2023/113 inaobi.xlsx
+++ b/LoanOfficer-A/2023/113 inaobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3200</v>
+        <v>4000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>20800</v>
+        <v>20000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1374,9 +1374,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45859</v>
+      </c>
+      <c r="C19" s="4">
+        <v>200</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1400,9 +1406,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45860</v>
+      </c>
+      <c r="C20" s="4">
+        <v>200</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1426,9 +1438,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45861</v>
+      </c>
+      <c r="C21" s="4">
+        <v>200</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1452,9 +1470,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45862</v>
+      </c>
+      <c r="C22" s="4">
+        <v>200</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>

--- a/LoanOfficer-A/2023/113 inaobi.xlsx
+++ b/LoanOfficer-A/2023/113 inaobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4000</v>
+        <v>4800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>20000</v>
+        <v>19200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1502,9 +1502,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45865</v>
+      </c>
+      <c r="C23" s="4">
+        <v>200</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1528,9 +1534,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45867</v>
+      </c>
+      <c r="C24" s="4">
+        <v>200</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1554,9 +1566,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45872</v>
+      </c>
+      <c r="C25" s="4">
+        <v>200</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1580,9 +1598,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45882</v>
+      </c>
+      <c r="C26" s="4">
+        <v>200</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>

--- a/LoanOfficer-A/2023/113 inaobi.xlsx
+++ b/LoanOfficer-A/2023/113 inaobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4800</v>
+        <v>5200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>19200</v>
+        <v>18800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1630,9 +1630,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45884</v>
+      </c>
+      <c r="C27" s="4">
+        <v>200</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1656,9 +1662,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45887</v>
+      </c>
+      <c r="C28" s="4">
+        <v>200</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>

--- a/LoanOfficer-A/2023/113 inaobi.xlsx
+++ b/LoanOfficer-A/2023/113 inaobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5200</v>
+        <v>6200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>18800</v>
+        <v>17800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45928</v>
+      </c>
+      <c r="G3" s="4">
+        <v>200</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -1694,9 +1700,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45903</v>
+      </c>
+      <c r="C29" s="4">
+        <v>200</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1720,9 +1732,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45907</v>
+      </c>
+      <c r="C30" s="4">
+        <v>200</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1746,9 +1764,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45919</v>
+      </c>
+      <c r="C31" s="4">
+        <v>200</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1772,9 +1796,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45925</v>
+      </c>
+      <c r="C32" s="4">
+        <v>200</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/113 inaobi.xlsx
+++ b/LoanOfficer-A/2023/113 inaobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>6200</v>
+        <v>7200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>17800</v>
+        <v>16800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -912,9 +912,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45932</v>
+      </c>
+      <c r="G4" s="4">
+        <v>200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -944,9 +950,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45942</v>
+      </c>
+      <c r="G5" s="4">
+        <v>200</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -976,9 +988,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45942</v>
+      </c>
+      <c r="G6" s="4">
+        <v>200</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1008,9 +1026,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45942</v>
+      </c>
+      <c r="G7" s="4">
+        <v>200</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1040,9 +1064,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45942</v>
+      </c>
+      <c r="G8" s="4">
+        <v>200</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>

--- a/LoanOfficer-A/2023/113 inaobi.xlsx
+++ b/LoanOfficer-A/2023/113 inaobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7200</v>
+        <v>7600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>16800</v>
+        <v>16400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1102,9 +1102,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45948</v>
+      </c>
+      <c r="G9" s="4">
+        <v>200</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1134,9 +1140,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45948</v>
+      </c>
+      <c r="G10" s="4">
+        <v>200</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>

--- a/LoanOfficer-A/2023/113 inaobi.xlsx
+++ b/LoanOfficer-A/2023/113 inaobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7600</v>
+        <v>8200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>16400</v>
+        <v>15800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1178,9 +1178,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45977</v>
+      </c>
+      <c r="G11" s="4">
+        <v>200</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1210,9 +1216,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45977</v>
+      </c>
+      <c r="G12" s="4">
+        <v>200</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1242,9 +1254,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45977</v>
+      </c>
+      <c r="G13" s="4">
+        <v>200</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
